--- a/Templates/LaborCardTemplate.xlsx
+++ b/Templates/LaborCardTemplate.xlsx
@@ -12,12 +12,12 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'&lt;fio&gt;'!$A$1:$J$26</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="162913" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t xml:space="preserve">Наименование работы (услуги): </t>
   </si>
@@ -41,6 +41,12 @@
     <t>(наименование структурного подразделения филиала (отдела, службы, группы)</t>
   </si>
   <si>
+    <t>&lt;workName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;specialCode&gt;</t>
+  </si>
+  <si>
     <t>&lt;programName&gt;</t>
   </si>
   <si>
@@ -113,6 +119,9 @@
     <t>(ФИО работника структурного подразделения)</t>
   </si>
   <si>
+    <t>&lt;num&gt;</t>
+  </si>
+  <si>
     <t>Понедельник</t>
   </si>
   <si>
@@ -132,6 +141,9 @@
   </si>
   <si>
     <t>Воскресенье</t>
+  </si>
+  <si>
+    <t>&lt;day&gt;</t>
   </si>
   <si>
     <r>
@@ -214,14 +226,17 @@
       <t xml:space="preserve">если номенклатурная работа разбивается на подзадачи и операции, не вошедшие в номенклатуру в ячейке временных затрат на работу указывается суммарное значение временных затрат на выполнение всех её подзадач и операций </t>
     </r>
   </si>
+  <si>
+    <t>Филиал АО "ЦЭНКИ" - Космический центр "Южный"</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[hh]:mm"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="166" formatCode="[hh]:mm"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yy;@"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -563,7 +578,7 @@
     <xf numFmtId="14" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -575,11 +590,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -622,9 +640,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -654,6 +669,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -972,16 +990,16 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="21"/>
+      <c r="I1" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="22"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="1"/>
       <c r="C2" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -1008,189 +1026,191 @@
       <c r="B4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
+      <c r="C4" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
+      <c r="C6" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="8"/>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
     </row>
     <row r="8" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
+      <c r="C8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
+      <c r="C9" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
     </row>
     <row r="10" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
+      <c r="C10" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
     </row>
     <row r="12" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
+        <v>18</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="8"/>
-      <c r="C13" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
+      <c r="C13" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
     </row>
     <row r="14" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
+        <v>20</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
-      <c r="C15" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
+      <c r="C15" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
     </row>
     <row r="16" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -1203,10 +1223,10 @@
       <c r="A17" s="5"/>
       <c r="B17" s="1"/>
       <c r="C17" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -1228,86 +1248,120 @@
       <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="26" t="s">
+      <c r="A19" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="35"/>
+    </row>
+    <row r="20" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="26"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="I20" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="34"/>
-    </row>
-    <row r="20" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="18" t="s">
+      <c r="J20" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="26"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
+      <c r="B22" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="19">
+        <v>0</v>
+      </c>
+      <c r="E22" s="19">
+        <v>0</v>
+      </c>
+      <c r="F22" s="19">
+        <v>0</v>
+      </c>
+      <c r="G22" s="19">
+        <v>0</v>
+      </c>
+      <c r="H22" s="19">
+        <v>0</v>
+      </c>
+      <c r="I22" s="19">
+        <v>0</v>
+      </c>
+      <c r="J22" s="19">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="1"/>
       <c r="C24" s="38" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D24" s="38"/>
       <c r="E24" s="38"/>
       <c r="F24" s="38"/>
       <c r="G24" s="39" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -1329,19 +1383,19 @@
       <c r="A26" s="5"/>
       <c r="B26" s="1"/>
       <c r="C26" s="36" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D26" s="36"/>
       <c r="E26" s="37" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F26" s="37"/>
       <c r="G26" s="36" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H26" s="36"/>
       <c r="I26" s="37" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J26" s="37"/>
     </row>
